--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -857,10 +857,23 @@
           <t>Austria</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Jordania</t>
         </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -892,10 +892,23 @@
           <t>Portugal</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
           <t>RD Congo</t>
         </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -917,10 +917,23 @@
           <t>Inglaterra</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Croacia</t>
         </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -942,10 +942,23 @@
           <t>Ghana</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -967,10 +967,23 @@
           <t>Uzbekistan</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -992,10 +992,23 @@
           <t>Republica Checa</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
           <t>Sudafrica</t>
         </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1017,10 +1017,23 @@
           <t>Suiza</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Bosnia y Herzegovina</t>
         </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1042,10 +1042,23 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1067,10 +1067,23 @@
           <t>Mexico</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Corea del Sur</t>
         </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1092,10 +1092,23 @@
           <t>Estados Unidos</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1117,10 +1117,23 @@
           <t>Escocia</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Marruecos</t>
         </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1142,10 +1142,23 @@
           <t>Brasil</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1179,10 +1179,23 @@
           <t>Paises Bajos</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
           <t>Suecia</t>
         </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1204,10 +1204,23 @@
           <t>Alemania</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Costa de Marfil</t>
         </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1238,10 +1238,23 @@
           <t>Ecuador</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1263,10 +1263,23 @@
           <t>Tunisia</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Japon</t>
         </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1288,10 +1288,23 @@
           <t>Espana</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
           <t>Arabia Saudita</t>
         </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1313,10 +1313,23 @@
           <t>Belgica</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1338,10 +1338,23 @@
           <t>Uruguay</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
           <t>Cabo Verde</t>
         </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1363,10 +1363,23 @@
           <t>Nueva Zelanda</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Egipto</t>
         </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1388,10 +1388,23 @@
           <t>Argentina</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1413,10 +1413,23 @@
           <t>Francia</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1438,10 +1438,23 @@
           <t>Noruega</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1463,10 +1463,23 @@
           <t>Jordania</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Argelia</t>
         </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1488,10 +1488,23 @@
           <t>Portugal</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1513,10 +1513,23 @@
           <t>Inglaterra</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1538,10 +1538,23 @@
           <t>Panama</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
           <t>Croacia</t>
         </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1563,10 +1563,23 @@
           <t>Colombia</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>RD Congo</t>
         </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1588,10 +1588,23 @@
           <t>Suiza</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1600,10 +1613,23 @@
           <t>Bosnia y Herzegovina</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1662,10 +1662,23 @@
           <t>Brasil</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
           <t>Escocia</t>
         </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1674,10 +1687,23 @@
           <t>Marruecos</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1638,10 +1638,23 @@
           <t>Mexico</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
           <t>Republica Checa</t>
         </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1650,10 +1663,23 @@
           <t>Sudafrica</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Corea del Sur</t>
         </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1762,10 +1762,23 @@
           <t>Alemania</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1774,10 +1787,23 @@
           <t>Curacao</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Costa de Marfil</t>
         </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1812,10 +1812,23 @@
           <t>Paises Bajos</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1824,10 +1837,23 @@
           <t>Japon</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Suecia</t>
         </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1750,10 +1750,23 @@
           <t>Paraguay</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1932,10 +1932,23 @@
           <t>Francia</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
           <t>Noruega</t>
         </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1957,10 +1957,23 @@
           <t>Senegal</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1920,10 +1920,23 @@
           <t>Cabo Verde</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Arabia Saudita</t>
         </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1908,10 +1908,23 @@
           <t>Espana</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1884,10 +1884,23 @@
           <t>Belgica</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
           <t>Nueva Zelanda</t>
         </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1909,10 +1909,23 @@
           <t>Egipto</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2034,10 +2034,23 @@
           <t>Panama</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2046,10 +2059,23 @@
           <t>Croacia</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2084,10 +2084,23 @@
           <t>Colombia</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2109,10 +2109,23 @@
           <t>Uzbekistan</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
           <t>RD Congo</t>
         </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2134,10 +2134,23 @@
           <t>Jordania</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2146,10 +2159,23 @@
           <t>Argelia</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2308,10 +2308,23 @@
           <t>Mexico</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2332,10 +2332,23 @@
           <t>Inglaterra</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>RD Congo</t>
         </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2374,10 +2374,23 @@
           <t>Estados Unidos</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Bosnia y Herzegovina</t>
         </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2411,10 +2411,23 @@
           <t>Portugal</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>Croacia</t>
         </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2437,10 +2437,23 @@
           <t>Suiza</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Argelia</t>
         </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2462,10 +2462,23 @@
           <t>Australia</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Egipto</t>
         </is>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2487,10 +2487,23 @@
           <t>Argentina</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Cabo Verde</t>
         </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2512,10 +2512,23 @@
           <t>Colombia</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2563,10 +2563,23 @@
           <t>Brasil</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Noruega</t>
         </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2626,10 +2626,23 @@
           <t>Estados Unidos</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
           <t>Belgica</t>
         </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2638,10 +2638,23 @@
           <t>Argentina</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Egipto</t>
         </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2689,10 +2689,23 @@
           <t>Francia</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Marruecos</t>
         </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2714,10 +2714,23 @@
           <t>Espana</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>Belgica</t>
         </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2739,10 +2739,23 @@
           <t>Noruega</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2764,10 +2764,23 @@
           <t>Argentina</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>Suiza</t>
         </is>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2773,10 +2773,23 @@
           <t>Francia</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Espana</t>
         </is>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -2794,10 +2794,23 @@
           <t>Argentina</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
